--- a/nr-update-bonne-pratique/ig/StructureDefinition-fr-core-observation-level-of-exertion.xlsx
+++ b/nr-update-bonne-pratique/ig/StructureDefinition-fr-core-observation-level-of-exertion.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-13T07:53:41+00:00</t>
+    <t>2025-05-13T08:17:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-update-bonne-pratique/ig/StructureDefinition-fr-core-observation-level-of-exertion.xlsx
+++ b/nr-update-bonne-pratique/ig/StructureDefinition-fr-core-observation-level-of-exertion.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-13T08:17:04+00:00</t>
+    <t>2025-05-13T08:20:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-update-bonne-pratique/ig/StructureDefinition-fr-core-observation-level-of-exertion.xlsx
+++ b/nr-update-bonne-pratique/ig/StructureDefinition-fr-core-observation-level-of-exertion.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-13T08:20:43+00:00</t>
+    <t>2025-05-13T08:21:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-update-bonne-pratique/ig/StructureDefinition-fr-core-observation-level-of-exertion.xlsx
+++ b/nr-update-bonne-pratique/ig/StructureDefinition-fr-core-observation-level-of-exertion.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-13T08:21:20+00:00</t>
+    <t>2025-05-13T08:21:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-update-bonne-pratique/ig/StructureDefinition-fr-core-observation-level-of-exertion.xlsx
+++ b/nr-update-bonne-pratique/ig/StructureDefinition-fr-core-observation-level-of-exertion.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-13T08:21:58+00:00</t>
+    <t>2025-05-20T13:28:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-update-bonne-pratique/ig/StructureDefinition-fr-core-observation-level-of-exertion.xlsx
+++ b/nr-update-bonne-pratique/ig/StructureDefinition-fr-core-observation-level-of-exertion.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-20T13:28:18+00:00</t>
+    <t>2025-05-20T13:33:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-update-bonne-pratique/ig/StructureDefinition-fr-core-observation-level-of-exertion.xlsx
+++ b/nr-update-bonne-pratique/ig/StructureDefinition-fr-core-observation-level-of-exertion.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-20T13:33:48+00:00</t>
+    <t>2025-05-20T13:49:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
